--- a/assets/units.xlsx
+++ b/assets/units.xlsx
@@ -184,6 +184,15 @@
   </si>
   <si>
     <t>Water soluble phosphorus</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>chemical</t>
+  </si>
+  <si>
+    <t>physical</t>
   </si>
 </sst>
 </file>
@@ -538,339 +547,462 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B41"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr defaultRowHeight="14.4" ns3:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="3" customFormat="1" ns3:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ns3:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ns3:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ns3:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ns3:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ns3:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ns3:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ns3:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ns3:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ns3:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ns3:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ns3:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ns3:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ns3:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ns3:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ns3:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ns3:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ns3:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="25.8" customHeight="1" ns3:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="35.4" customHeight="1" ns3:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ns3:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ns3:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ns3:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ns3:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ns3:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C25" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ns3:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ns3:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" ht="24" x14ac:dyDescent="0.3">
+      <c r="C27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="24" ns3:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" ht="24" x14ac:dyDescent="0.3">
+      <c r="C28" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="24" ns3:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C29" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ns3:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C30" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ns3:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ns3:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C32" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ns3:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C33" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ns3:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C34" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ns3:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C35" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ns3:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C36" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ns3:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C37" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ns3:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" ht="24" x14ac:dyDescent="0.3">
+      <c r="C38" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="24" ns3:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C39" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ns3:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" ht="24" x14ac:dyDescent="0.3">
+      <c r="C40" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="24" ns3:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="C41" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
